--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Challenge League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Challenge League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="215">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,15 +427,15 @@
     <t>['63', '90+5']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['29', '86']</t>
   </si>
   <si>
-    <t>['8']</t>
-  </si>
-  <si>
-    <t>['59']</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -454,6 +454,18 @@
     <t>['10', '58', '83']</t>
   </si>
   <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['41', '46', '68']</t>
+  </si>
+  <si>
     <t>['25', '90+2']</t>
   </si>
   <si>
@@ -463,9 +475,6 @@
     <t>['7', '44', '83']</t>
   </si>
   <si>
-    <t>['28']</t>
-  </si>
-  <si>
     <t>['4']</t>
   </si>
   <si>
@@ -616,12 +625,12 @@
     <t>['18', '24']</t>
   </si>
   <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
     <t>['40']</t>
   </si>
   <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
     <t>['45+3']</t>
   </si>
   <si>
@@ -631,19 +640,25 @@
     <t>['29', '53']</t>
   </si>
   <si>
-    <t>['30']</t>
-  </si>
-  <si>
     <t>['87']</t>
   </si>
   <si>
     <t>['33', '69', '79']</t>
   </si>
   <si>
+    <t>['41', '75']</t>
+  </si>
+  <si>
     <t>['29', '78']</t>
   </si>
   <si>
-    <t>['41', '75']</t>
+    <t>['34', '76']</t>
+  </si>
+  <si>
+    <t>['86', '90+3']</t>
+  </si>
+  <si>
+    <t>['56']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1261,7 +1276,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1339,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1467,7 +1482,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1673,7 +1688,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>3.75</v>
@@ -1960,7 +1975,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2291,7 +2306,7 @@
         <v>84</v>
       </c>
       <c r="P7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q7">
         <v>2.63</v>
@@ -2497,7 +2512,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q8">
         <v>2.63</v>
@@ -2575,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -2781,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9">
         <v>1.33</v>
@@ -2909,7 +2924,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -2990,7 +3005,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3193,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3321,7 +3336,7 @@
         <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q12">
         <v>2.88</v>
@@ -3399,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
         <v>1.22</v>
@@ -3527,7 +3542,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q13">
         <v>2.2</v>
@@ -3605,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.92</v>
@@ -3733,7 +3748,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -3939,7 +3954,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4145,7 +4160,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4226,7 +4241,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR16">
         <v>1.95</v>
@@ -4351,7 +4366,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4432,7 +4447,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR17">
         <v>1.81</v>
@@ -4557,7 +4572,7 @@
         <v>84</v>
       </c>
       <c r="P18" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q18">
         <v>3.1</v>
@@ -4635,7 +4650,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ18">
         <v>1.78</v>
@@ -4763,7 +4778,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q19">
         <v>2.3</v>
@@ -4841,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
         <v>1.33</v>
@@ -4969,7 +4984,7 @@
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -5175,7 +5190,7 @@
         <v>95</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5256,7 +5271,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ21">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR21">
         <v>1.63</v>
@@ -5587,7 +5602,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5999,7 +6014,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6080,7 +6095,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.92</v>
@@ -6205,7 +6220,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6283,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>0.89</v>
@@ -6411,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -6489,10 +6504,10 @@
         <v>0.5</v>
       </c>
       <c r="AP27">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ27">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR27">
         <v>1.47</v>
@@ -6617,7 +6632,7 @@
         <v>84</v>
       </c>
       <c r="P28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>3</v>
@@ -6695,10 +6710,10 @@
         <v>0.33</v>
       </c>
       <c r="AP28">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.43</v>
@@ -6901,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7029,7 +7044,7 @@
         <v>102</v>
       </c>
       <c r="P30" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7235,7 +7250,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7522,7 +7537,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -7647,7 +7662,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q33">
         <v>3.2</v>
@@ -7725,7 +7740,7 @@
         <v>1.33</v>
       </c>
       <c r="AP33">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>1.11</v>
@@ -7853,7 +7868,7 @@
         <v>105</v>
       </c>
       <c r="P34" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8059,7 +8074,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8137,7 +8152,7 @@
         <v>1.33</v>
       </c>
       <c r="AP35">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -8265,7 +8280,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8346,7 +8361,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR36">
         <v>2.16</v>
@@ -8471,7 +8486,7 @@
         <v>108</v>
       </c>
       <c r="P37" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -8549,7 +8564,7 @@
         <v>1.33</v>
       </c>
       <c r="AP37">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ37">
         <v>0.89</v>
@@ -8883,7 +8898,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9089,7 +9104,7 @@
         <v>110</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9170,7 +9185,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.35</v>
@@ -9373,10 +9388,10 @@
         <v>0.33</v>
       </c>
       <c r="AP41">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ41">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR41">
         <v>1.58</v>
@@ -9501,7 +9516,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>3</v>
@@ -9707,7 +9722,7 @@
         <v>84</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>3</v>
@@ -9788,7 +9803,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR43">
         <v>1.64</v>
@@ -9913,7 +9928,7 @@
         <v>95</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -9991,10 +10006,10 @@
         <v>1.67</v>
       </c>
       <c r="AP44">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10197,7 +10212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.33</v>
@@ -10325,7 +10340,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10531,7 +10546,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10609,7 +10624,7 @@
         <v>2.25</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ47">
         <v>1.22</v>
@@ -10943,7 +10958,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>2.5</v>
@@ -11021,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ49">
         <v>0.89</v>
@@ -11230,7 +11245,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ50">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR50">
         <v>1.24</v>
@@ -11355,7 +11370,7 @@
         <v>117</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>2.75</v>
@@ -11436,7 +11451,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ51">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.86</v>
@@ -11561,7 +11576,7 @@
         <v>84</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.63</v>
@@ -11639,7 +11654,7 @@
         <v>1.4</v>
       </c>
       <c r="AP52">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ52">
         <v>1.11</v>
@@ -11767,7 +11782,7 @@
         <v>118</v>
       </c>
       <c r="P53" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -11845,10 +11860,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR53">
         <v>1.54</v>
@@ -11973,7 +11988,7 @@
         <v>84</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12054,7 +12069,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR54">
         <v>1.69</v>
@@ -12179,7 +12194,7 @@
         <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12591,7 +12606,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12669,10 +12684,10 @@
         <v>0.83</v>
       </c>
       <c r="AP57">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ57">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.74</v>
@@ -13003,7 +13018,7 @@
         <v>84</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13290,7 +13305,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ60">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>1.75</v>
@@ -13415,7 +13430,7 @@
         <v>121</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13493,7 +13508,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1.22</v>
@@ -13621,7 +13636,7 @@
         <v>122</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
@@ -13699,10 +13714,10 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR62">
         <v>1.61</v>
@@ -14033,7 +14048,7 @@
         <v>124</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q64">
         <v>2.4</v>
@@ -14114,7 +14129,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ64">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.41</v>
@@ -14317,10 +14332,10 @@
         <v>2.2</v>
       </c>
       <c r="AP65">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ65">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR65">
         <v>1.81</v>
@@ -14445,7 +14460,7 @@
         <v>126</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14523,7 +14538,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>1.78</v>
@@ -14651,7 +14666,7 @@
         <v>127</v>
       </c>
       <c r="P67" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14857,7 +14872,7 @@
         <v>128</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15063,7 +15078,7 @@
         <v>129</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15144,7 +15159,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR69">
         <v>1.4</v>
@@ -15269,7 +15284,7 @@
         <v>130</v>
       </c>
       <c r="P70" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q70">
         <v>2.25</v>
@@ -15347,7 +15362,7 @@
         <v>1.67</v>
       </c>
       <c r="AP70">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>1.11</v>
@@ -15475,7 +15490,7 @@
         <v>131</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15681,7 +15696,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
@@ -15759,7 +15774,7 @@
         <v>1.14</v>
       </c>
       <c r="AP72">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -15887,7 +15902,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -15965,7 +15980,7 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ73">
         <v>1.78</v>
@@ -16093,7 +16108,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>2.3</v>
@@ -16174,7 +16189,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR74">
         <v>1.53</v>
@@ -16299,7 +16314,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.38</v>
@@ -16505,7 +16520,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -16669,7 +16684,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>7487414</v>
+        <v>7487412</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -16684,151 +16699,151 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I77">
         <v>1</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O77" t="s">
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="Q77">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S77">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T77">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="U77">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="V77">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="W77">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="X77">
-        <v>6.25</v>
+        <v>4.95</v>
       </c>
       <c r="Y77">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z77">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="AA77">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="AB77">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="AC77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE77">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AH77">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AI77">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ77">
+        <v>2.38</v>
+      </c>
+      <c r="AK77">
+        <v>1.22</v>
+      </c>
+      <c r="AL77">
+        <v>1.21</v>
+      </c>
+      <c r="AM77">
+        <v>1.73</v>
+      </c>
+      <c r="AN77">
+        <v>2.29</v>
+      </c>
+      <c r="AO77">
+        <v>2</v>
+      </c>
+      <c r="AP77">
+        <v>2</v>
+      </c>
+      <c r="AQ77">
         <v>2.1</v>
       </c>
-      <c r="AK77">
-        <v>1.39</v>
-      </c>
-      <c r="AL77">
-        <v>1.25</v>
-      </c>
-      <c r="AM77">
-        <v>1.43</v>
-      </c>
-      <c r="AN77">
-        <v>1.14</v>
-      </c>
-      <c r="AO77">
-        <v>1.43</v>
-      </c>
-      <c r="AP77">
-        <v>1.22</v>
-      </c>
-      <c r="AQ77">
-        <v>1.11</v>
-      </c>
       <c r="AR77">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AS77">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AT77">
-        <v>3.43</v>
+        <v>3.66</v>
       </c>
       <c r="AU77">
         <v>4</v>
       </c>
       <c r="AV77">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AW77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX77">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY77">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ77">
         <v>18</v>
       </c>
       <c r="BA77">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BB77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC77">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD77">
         <v>0</v>
@@ -16852,7 +16867,7 @@
         <v>0</v>
       </c>
       <c r="BK77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BL77">
         <v>0</v>
@@ -16875,7 +16890,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7487412</v>
+        <v>7487410</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -16890,19 +16905,19 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -16917,124 +16932,124 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="Q78">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T78">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="U78">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="V78">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="W78">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="X78">
-        <v>4.95</v>
+        <v>5.95</v>
       </c>
       <c r="Y78">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z78">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AA78">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="AB78">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="AC78">
         <v>1.01</v>
       </c>
       <c r="AD78">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE78">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AG78">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AH78">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AI78">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ78">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AK78">
+        <v>1.21</v>
+      </c>
+      <c r="AL78">
         <v>1.22</v>
-      </c>
-      <c r="AL78">
-        <v>1.21</v>
       </c>
       <c r="AM78">
         <v>1.73</v>
       </c>
       <c r="AN78">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="AO78">
-        <v>2</v>
+        <v>0.57</v>
       </c>
       <c r="AP78">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>0.89</v>
       </c>
       <c r="AR78">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AS78">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AT78">
-        <v>3.66</v>
+        <v>2.77</v>
       </c>
       <c r="AU78">
+        <v>6</v>
+      </c>
+      <c r="AV78">
         <v>4</v>
       </c>
-      <c r="AV78">
-        <v>7</v>
-      </c>
       <c r="AW78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX78">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AY78">
         <v>13</v>
       </c>
       <c r="AZ78">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BA78">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BB78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC78">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD78">
         <v>0</v>
@@ -17058,7 +17073,7 @@
         <v>0</v>
       </c>
       <c r="BK78">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BL78">
         <v>0</v>
@@ -17081,7 +17096,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>7487410</v>
+        <v>7487414</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -17096,88 +17111,88 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79">
         <v>1</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" t="s">
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q79">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="T79">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U79">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="V79">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="W79">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X79">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="Y79">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="AA79">
         <v>3.09</v>
       </c>
       <c r="AB79">
-        <v>3.29</v>
+        <v>2.45</v>
       </c>
       <c r="AC79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD79">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF79">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AG79">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH79">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AI79">
         <v>1.67</v>
@@ -17186,58 +17201,58 @@
         <v>2.1</v>
       </c>
       <c r="AK79">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AL79">
+        <v>1.25</v>
+      </c>
+      <c r="AM79">
+        <v>1.43</v>
+      </c>
+      <c r="AN79">
+        <v>1.14</v>
+      </c>
+      <c r="AO79">
+        <v>1.43</v>
+      </c>
+      <c r="AP79">
         <v>1.22</v>
       </c>
-      <c r="AM79">
-        <v>1.73</v>
-      </c>
-      <c r="AN79">
-        <v>1.57</v>
-      </c>
-      <c r="AO79">
-        <v>0.57</v>
-      </c>
-      <c r="AP79">
-        <v>1.33</v>
-      </c>
       <c r="AQ79">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AR79">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="AS79">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AT79">
-        <v>2.77</v>
+        <v>3.43</v>
       </c>
       <c r="AU79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV79">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AW79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX79">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY79">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ79">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BA79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC79">
         <v>6</v>
@@ -17407,10 +17422,10 @@
         <v>0.57</v>
       </c>
       <c r="AP80">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR80">
         <v>1.62</v>
@@ -17535,7 +17550,7 @@
         <v>141</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>3.6</v>
@@ -17613,7 +17628,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
         <v>1.33</v>
@@ -17741,7 +17756,7 @@
         <v>84</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>2.05</v>
@@ -17819,10 +17834,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR82">
         <v>1.78</v>
@@ -18025,7 +18040,7 @@
         <v>1.38</v>
       </c>
       <c r="AP83">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ83">
         <v>1.22</v>
@@ -18234,7 +18249,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.62</v>
@@ -18359,7 +18374,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>2.63</v>
@@ -18440,7 +18455,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18565,7 +18580,7 @@
         <v>84</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="Q86">
         <v>2.3</v>
@@ -18771,7 +18786,7 @@
         <v>144</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>3.1</v>
@@ -18977,7 +18992,7 @@
         <v>105</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q88">
         <v>3.1</v>
@@ -19055,10 +19070,10 @@
         <v>1.88</v>
       </c>
       <c r="AP88">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ88">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR88">
         <v>1.6</v>
@@ -19141,7 +19156,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>7487424</v>
+        <v>7487423</v>
       </c>
       <c r="C89" t="s">
         <v>68</v>
@@ -19156,190 +19171,190 @@
         <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H89" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89">
         <v>1</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M89">
         <v>2</v>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O89" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T89">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="U89">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="V89">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="W89">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X89">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="AA89">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB89">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="AC89">
         <v>1.01</v>
       </c>
       <c r="AD89">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="AE89">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AG89">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AH89">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AI89">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ89">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AK89">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AL89">
         <v>1.25</v>
       </c>
       <c r="AM89">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AN89">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AO89">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.22</v>
+        <v>2.22</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AR89">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AS89">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AT89">
-        <v>3.18</v>
+        <v>3.73</v>
       </c>
       <c r="AU89">
+        <v>6</v>
+      </c>
+      <c r="AV89">
         <v>7</v>
       </c>
-      <c r="AV89">
+      <c r="AW89">
+        <v>7</v>
+      </c>
+      <c r="AX89">
+        <v>4</v>
+      </c>
+      <c r="AY89">
+        <v>15</v>
+      </c>
+      <c r="AZ89">
+        <v>14</v>
+      </c>
+      <c r="BA89">
+        <v>3</v>
+      </c>
+      <c r="BB89">
+        <v>2</v>
+      </c>
+      <c r="BC89">
         <v>5</v>
       </c>
-      <c r="AW89">
-        <v>5</v>
-      </c>
-      <c r="AX89">
-        <v>2</v>
-      </c>
-      <c r="AY89">
-        <v>12</v>
-      </c>
-      <c r="AZ89">
-        <v>8</v>
-      </c>
-      <c r="BA89">
-        <v>6</v>
-      </c>
-      <c r="BB89">
-        <v>3</v>
-      </c>
-      <c r="BC89">
-        <v>9</v>
-      </c>
       <c r="BD89">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="BE89">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="BF89">
-        <v>2.95</v>
+        <v>1.81</v>
       </c>
       <c r="BG89">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="BH89">
-        <v>2.28</v>
+        <v>3.14</v>
       </c>
       <c r="BI89">
+        <v>1.51</v>
+      </c>
+      <c r="BJ89">
+        <v>2.26</v>
+      </c>
+      <c r="BK89">
         <v>1.91</v>
       </c>
-      <c r="BJ89">
+      <c r="BL89">
         <v>1.76</v>
       </c>
-      <c r="BK89">
-        <v>2.52</v>
-      </c>
-      <c r="BL89">
-        <v>1.41</v>
-      </c>
       <c r="BM89">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="BN89">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="BO89">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BP89">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="90" spans="1:68">
@@ -19347,7 +19362,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>7487423</v>
+        <v>7487424</v>
       </c>
       <c r="C90" t="s">
         <v>68</v>
@@ -19362,190 +19377,1014 @@
         <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90">
         <v>1</v>
       </c>
       <c r="K90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M90">
         <v>2</v>
       </c>
       <c r="N90">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O90" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q90">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="R90">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
+        <v>4</v>
+      </c>
+      <c r="T90">
+        <v>1.38</v>
+      </c>
+      <c r="U90">
+        <v>2.9</v>
+      </c>
+      <c r="V90">
         <v>2.75</v>
       </c>
-      <c r="T90">
-        <v>1.29</v>
-      </c>
-      <c r="U90">
-        <v>3.4</v>
-      </c>
-      <c r="V90">
-        <v>2.36</v>
-      </c>
       <c r="W90">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X90">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="AA90">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB90">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="AC90">
         <v>1.01</v>
       </c>
       <c r="AD90">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="AE90">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="AG90">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AH90">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AI90">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ90">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AK90">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AL90">
         <v>1.25</v>
       </c>
       <c r="AM90">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AN90">
-        <v>2.13</v>
+        <v>1.38</v>
       </c>
       <c r="AO90">
+        <v>1.13</v>
+      </c>
+      <c r="AP90">
+        <v>1.22</v>
+      </c>
+      <c r="AQ90">
+        <v>1.33</v>
+      </c>
+      <c r="AR90">
+        <v>1.61</v>
+      </c>
+      <c r="AS90">
+        <v>1.57</v>
+      </c>
+      <c r="AT90">
+        <v>3.18</v>
+      </c>
+      <c r="AU90">
+        <v>7</v>
+      </c>
+      <c r="AV90">
+        <v>5</v>
+      </c>
+      <c r="AW90">
+        <v>5</v>
+      </c>
+      <c r="AX90">
+        <v>2</v>
+      </c>
+      <c r="AY90">
+        <v>12</v>
+      </c>
+      <c r="AZ90">
+        <v>8</v>
+      </c>
+      <c r="BA90">
+        <v>6</v>
+      </c>
+      <c r="BB90">
+        <v>3</v>
+      </c>
+      <c r="BC90">
+        <v>9</v>
+      </c>
+      <c r="BD90">
+        <v>1.59</v>
+      </c>
+      <c r="BE90">
+        <v>6.65</v>
+      </c>
+      <c r="BF90">
+        <v>2.95</v>
+      </c>
+      <c r="BG90">
+        <v>1.5</v>
+      </c>
+      <c r="BH90">
+        <v>2.28</v>
+      </c>
+      <c r="BI90">
+        <v>1.91</v>
+      </c>
+      <c r="BJ90">
+        <v>1.76</v>
+      </c>
+      <c r="BK90">
+        <v>2.52</v>
+      </c>
+      <c r="BL90">
+        <v>1.41</v>
+      </c>
+      <c r="BM90">
+        <v>3.5</v>
+      </c>
+      <c r="BN90">
+        <v>1.22</v>
+      </c>
+      <c r="BO90">
+        <v>0</v>
+      </c>
+      <c r="BP90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7776402</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45681.64583333334</v>
+      </c>
+      <c r="F91">
+        <v>19</v>
+      </c>
+      <c r="G91" t="s">
+        <v>70</v>
+      </c>
+      <c r="H91" t="s">
+        <v>75</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>2</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>3</v>
+      </c>
+      <c r="O91" t="s">
+        <v>146</v>
+      </c>
+      <c r="P91" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q91">
+        <v>2.88</v>
+      </c>
+      <c r="R91">
+        <v>2.3</v>
+      </c>
+      <c r="S91">
+        <v>3</v>
+      </c>
+      <c r="T91">
+        <v>1.28</v>
+      </c>
+      <c r="U91">
+        <v>3.46</v>
+      </c>
+      <c r="V91">
+        <v>2.22</v>
+      </c>
+      <c r="W91">
+        <v>1.6</v>
+      </c>
+      <c r="X91">
+        <v>5.25</v>
+      </c>
+      <c r="Y91">
+        <v>1.14</v>
+      </c>
+      <c r="Z91">
+        <v>2.45</v>
+      </c>
+      <c r="AA91">
+        <v>3.5</v>
+      </c>
+      <c r="AB91">
+        <v>2.55</v>
+      </c>
+      <c r="AC91">
+        <v>1.01</v>
+      </c>
+      <c r="AD91">
+        <v>13</v>
+      </c>
+      <c r="AE91">
+        <v>1.17</v>
+      </c>
+      <c r="AF91">
+        <v>4.6</v>
+      </c>
+      <c r="AG91">
+        <v>1.62</v>
+      </c>
+      <c r="AH91">
+        <v>2.25</v>
+      </c>
+      <c r="AI91">
+        <v>1.53</v>
+      </c>
+      <c r="AJ91">
+        <v>2.38</v>
+      </c>
+      <c r="AK91">
+        <v>1.34</v>
+      </c>
+      <c r="AL91">
         <v>1.25</v>
       </c>
-      <c r="AP90">
+      <c r="AM91">
+        <v>1.57</v>
+      </c>
+      <c r="AN91">
+        <v>1.44</v>
+      </c>
+      <c r="AO91">
+        <v>0.75</v>
+      </c>
+      <c r="AP91">
+        <v>1.3</v>
+      </c>
+      <c r="AQ91">
+        <v>1</v>
+      </c>
+      <c r="AR91">
+        <v>1.62</v>
+      </c>
+      <c r="AS91">
+        <v>1.61</v>
+      </c>
+      <c r="AT91">
+        <v>3.23</v>
+      </c>
+      <c r="AU91">
+        <v>5</v>
+      </c>
+      <c r="AV91">
+        <v>6</v>
+      </c>
+      <c r="AW91">
+        <v>2</v>
+      </c>
+      <c r="AX91">
+        <v>10</v>
+      </c>
+      <c r="AY91">
+        <v>7</v>
+      </c>
+      <c r="AZ91">
+        <v>16</v>
+      </c>
+      <c r="BA91">
+        <v>4</v>
+      </c>
+      <c r="BB91">
+        <v>5</v>
+      </c>
+      <c r="BC91">
+        <v>9</v>
+      </c>
+      <c r="BD91">
+        <v>1.87</v>
+      </c>
+      <c r="BE91">
+        <v>6.15</v>
+      </c>
+      <c r="BF91">
+        <v>2.38</v>
+      </c>
+      <c r="BG91">
+        <v>1.25</v>
+      </c>
+      <c r="BH91">
+        <v>3.28</v>
+      </c>
+      <c r="BI91">
+        <v>1.55</v>
+      </c>
+      <c r="BJ91">
+        <v>2.35</v>
+      </c>
+      <c r="BK91">
+        <v>1.92</v>
+      </c>
+      <c r="BL91">
+        <v>1.87</v>
+      </c>
+      <c r="BM91">
+        <v>2.43</v>
+      </c>
+      <c r="BN91">
+        <v>1.52</v>
+      </c>
+      <c r="BO91">
+        <v>3.2</v>
+      </c>
+      <c r="BP91">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7776403</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45681.64583333334</v>
+      </c>
+      <c r="F92">
+        <v>19</v>
+      </c>
+      <c r="G92" t="s">
+        <v>76</v>
+      </c>
+      <c r="H92" t="s">
+        <v>72</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92">
+        <v>3</v>
+      </c>
+      <c r="O92" t="s">
+        <v>147</v>
+      </c>
+      <c r="P92" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q92">
+        <v>4.75</v>
+      </c>
+      <c r="R92">
+        <v>2.3</v>
+      </c>
+      <c r="S92">
+        <v>2.2</v>
+      </c>
+      <c r="T92">
+        <v>1.3</v>
+      </c>
+      <c r="U92">
+        <v>3.32</v>
+      </c>
+      <c r="V92">
+        <v>2.31</v>
+      </c>
+      <c r="W92">
+        <v>1.56</v>
+      </c>
+      <c r="X92">
+        <v>5.55</v>
+      </c>
+      <c r="Y92">
+        <v>1.12</v>
+      </c>
+      <c r="Z92">
+        <v>4.5</v>
+      </c>
+      <c r="AA92">
+        <v>3.9</v>
+      </c>
+      <c r="AB92">
+        <v>1.65</v>
+      </c>
+      <c r="AC92">
+        <v>1.01</v>
+      </c>
+      <c r="AD92">
+        <v>11</v>
+      </c>
+      <c r="AE92">
+        <v>1.19</v>
+      </c>
+      <c r="AF92">
+        <v>4.4</v>
+      </c>
+      <c r="AG92">
+        <v>1.7</v>
+      </c>
+      <c r="AH92">
+        <v>2.1</v>
+      </c>
+      <c r="AI92">
+        <v>1.73</v>
+      </c>
+      <c r="AJ92">
+        <v>2</v>
+      </c>
+      <c r="AK92">
+        <v>1.73</v>
+      </c>
+      <c r="AL92">
+        <v>1.25</v>
+      </c>
+      <c r="AM92">
+        <v>1.25</v>
+      </c>
+      <c r="AN92">
+        <v>1.11</v>
+      </c>
+      <c r="AO92">
+        <v>2</v>
+      </c>
+      <c r="AP92">
+        <v>1</v>
+      </c>
+      <c r="AQ92">
+        <v>2.1</v>
+      </c>
+      <c r="AR92">
+        <v>1.59</v>
+      </c>
+      <c r="AS92">
+        <v>1.8</v>
+      </c>
+      <c r="AT92">
+        <v>3.39</v>
+      </c>
+      <c r="AU92">
+        <v>4</v>
+      </c>
+      <c r="AV92">
+        <v>7</v>
+      </c>
+      <c r="AW92">
+        <v>8</v>
+      </c>
+      <c r="AX92">
+        <v>9</v>
+      </c>
+      <c r="AY92">
+        <v>12</v>
+      </c>
+      <c r="AZ92">
+        <v>16</v>
+      </c>
+      <c r="BA92">
+        <v>1</v>
+      </c>
+      <c r="BB92">
+        <v>14</v>
+      </c>
+      <c r="BC92">
+        <v>15</v>
+      </c>
+      <c r="BD92">
+        <v>2.82</v>
+      </c>
+      <c r="BE92">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF92">
+        <v>1.56</v>
+      </c>
+      <c r="BG92">
+        <v>1.29</v>
+      </c>
+      <c r="BH92">
+        <v>3.04</v>
+      </c>
+      <c r="BI92">
+        <v>1.35</v>
+      </c>
+      <c r="BJ92">
+        <v>2.74</v>
+      </c>
+      <c r="BK92">
+        <v>2.38</v>
+      </c>
+      <c r="BL92">
+        <v>2.1</v>
+      </c>
+      <c r="BM92">
+        <v>2.11</v>
+      </c>
+      <c r="BN92">
+        <v>1.69</v>
+      </c>
+      <c r="BO92">
+        <v>2.69</v>
+      </c>
+      <c r="BP92">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7776404</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45681.67708333334</v>
+      </c>
+      <c r="F93">
+        <v>19</v>
+      </c>
+      <c r="G93" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" t="s">
+        <v>78</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93" t="s">
+        <v>148</v>
+      </c>
+      <c r="P93" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q93">
+        <v>2.38</v>
+      </c>
+      <c r="R93">
+        <v>2.2</v>
+      </c>
+      <c r="S93">
+        <v>4.33</v>
+      </c>
+      <c r="T93">
+        <v>1.33</v>
+      </c>
+      <c r="U93">
+        <v>3.12</v>
+      </c>
+      <c r="V93">
+        <v>2.45</v>
+      </c>
+      <c r="W93">
+        <v>1.49</v>
+      </c>
+      <c r="X93">
+        <v>6.15</v>
+      </c>
+      <c r="Y93">
+        <v>1.1</v>
+      </c>
+      <c r="Z93">
+        <v>1.8</v>
+      </c>
+      <c r="AA93">
+        <v>3.6</v>
+      </c>
+      <c r="AB93">
+        <v>4.2</v>
+      </c>
+      <c r="AC93">
+        <v>1.01</v>
+      </c>
+      <c r="AD93">
+        <v>11</v>
+      </c>
+      <c r="AE93">
+        <v>1.23</v>
+      </c>
+      <c r="AF93">
+        <v>3.95</v>
+      </c>
+      <c r="AG93">
+        <v>1.85</v>
+      </c>
+      <c r="AH93">
+        <v>1.95</v>
+      </c>
+      <c r="AI93">
+        <v>1.73</v>
+      </c>
+      <c r="AJ93">
+        <v>2</v>
+      </c>
+      <c r="AK93">
+        <v>1.29</v>
+      </c>
+      <c r="AL93">
+        <v>1.27</v>
+      </c>
+      <c r="AM93">
+        <v>1.62</v>
+      </c>
+      <c r="AN93">
         <v>2.22</v>
       </c>
-      <c r="AQ90">
-        <v>1.11</v>
-      </c>
-      <c r="AR90">
-        <v>1.97</v>
-      </c>
-      <c r="AS90">
-        <v>1.76</v>
-      </c>
-      <c r="AT90">
-        <v>3.73</v>
-      </c>
-      <c r="AU90">
+      <c r="AO93">
+        <v>1.22</v>
+      </c>
+      <c r="AP93">
+        <v>2.1</v>
+      </c>
+      <c r="AQ93">
+        <v>1.2</v>
+      </c>
+      <c r="AR93">
+        <v>1.57</v>
+      </c>
+      <c r="AS93">
+        <v>1.25</v>
+      </c>
+      <c r="AT93">
+        <v>2.82</v>
+      </c>
+      <c r="AU93">
+        <v>9</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>7</v>
+      </c>
+      <c r="AX93">
         <v>6</v>
       </c>
-      <c r="AV90">
+      <c r="AY93">
+        <v>16</v>
+      </c>
+      <c r="AZ93">
+        <v>11</v>
+      </c>
+      <c r="BA93">
+        <v>5</v>
+      </c>
+      <c r="BB93">
+        <v>1</v>
+      </c>
+      <c r="BC93">
+        <v>6</v>
+      </c>
+      <c r="BD93">
+        <v>1.52</v>
+      </c>
+      <c r="BE93">
+        <v>7.8</v>
+      </c>
+      <c r="BF93">
+        <v>3.02</v>
+      </c>
+      <c r="BG93">
+        <v>1.5</v>
+      </c>
+      <c r="BH93">
+        <v>2.47</v>
+      </c>
+      <c r="BI93">
+        <v>1.88</v>
+      </c>
+      <c r="BJ93">
+        <v>1.92</v>
+      </c>
+      <c r="BK93">
+        <v>2.36</v>
+      </c>
+      <c r="BL93">
+        <v>1.55</v>
+      </c>
+      <c r="BM93">
+        <v>3.2</v>
+      </c>
+      <c r="BN93">
+        <v>1.26</v>
+      </c>
+      <c r="BO93">
+        <v>4.95</v>
+      </c>
+      <c r="BP93">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7776406</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45681.67708333334</v>
+      </c>
+      <c r="F94">
+        <v>19</v>
+      </c>
+      <c r="G94" t="s">
+        <v>79</v>
+      </c>
+      <c r="H94" t="s">
+        <v>74</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>3</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>4</v>
+      </c>
+      <c r="O94" t="s">
+        <v>149</v>
+      </c>
+      <c r="P94" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q94">
+        <v>2.2</v>
+      </c>
+      <c r="R94">
+        <v>2.3</v>
+      </c>
+      <c r="S94">
+        <v>4.5</v>
+      </c>
+      <c r="T94">
+        <v>1.27</v>
+      </c>
+      <c r="U94">
+        <v>3.54</v>
+      </c>
+      <c r="V94">
+        <v>2.19</v>
+      </c>
+      <c r="W94">
+        <v>1.62</v>
+      </c>
+      <c r="X94">
+        <v>5.15</v>
+      </c>
+      <c r="Y94">
+        <v>1.14</v>
+      </c>
+      <c r="Z94">
+        <v>1.65</v>
+      </c>
+      <c r="AA94">
+        <v>3.9</v>
+      </c>
+      <c r="AB94">
+        <v>4.75</v>
+      </c>
+      <c r="AC94">
+        <v>1.01</v>
+      </c>
+      <c r="AD94">
+        <v>13</v>
+      </c>
+      <c r="AE94">
+        <v>1.13</v>
+      </c>
+      <c r="AF94">
+        <v>5.2</v>
+      </c>
+      <c r="AG94">
+        <v>1.67</v>
+      </c>
+      <c r="AH94">
+        <v>2.15</v>
+      </c>
+      <c r="AI94">
+        <v>1.73</v>
+      </c>
+      <c r="AJ94">
+        <v>2</v>
+      </c>
+      <c r="AK94">
+        <v>1.22</v>
+      </c>
+      <c r="AL94">
+        <v>1.22</v>
+      </c>
+      <c r="AM94">
+        <v>1.84</v>
+      </c>
+      <c r="AN94">
+        <v>1.89</v>
+      </c>
+      <c r="AO94">
+        <v>0.89</v>
+      </c>
+      <c r="AP94">
+        <v>2</v>
+      </c>
+      <c r="AQ94">
+        <v>0.8</v>
+      </c>
+      <c r="AR94">
+        <v>1.69</v>
+      </c>
+      <c r="AS94">
+        <v>1.26</v>
+      </c>
+      <c r="AT94">
+        <v>2.95</v>
+      </c>
+      <c r="AU94">
         <v>7</v>
       </c>
-      <c r="AW90">
-        <v>7</v>
-      </c>
-      <c r="AX90">
-        <v>4</v>
-      </c>
-      <c r="AY90">
+      <c r="AV94">
+        <v>3</v>
+      </c>
+      <c r="AW94">
+        <v>8</v>
+      </c>
+      <c r="AX94">
+        <v>3</v>
+      </c>
+      <c r="AY94">
         <v>15</v>
       </c>
-      <c r="AZ90">
-        <v>14</v>
-      </c>
-      <c r="BA90">
+      <c r="AZ94">
+        <v>6</v>
+      </c>
+      <c r="BA94">
+        <v>6</v>
+      </c>
+      <c r="BB94">
         <v>3</v>
       </c>
-      <c r="BB90">
-        <v>2</v>
-      </c>
-      <c r="BC90">
-        <v>5</v>
-      </c>
-      <c r="BD90">
-        <v>2.4</v>
-      </c>
-      <c r="BE90">
-        <v>6.7</v>
-      </c>
-      <c r="BF90">
-        <v>1.81</v>
-      </c>
-      <c r="BG90">
-        <v>1.27</v>
-      </c>
-      <c r="BH90">
-        <v>3.14</v>
-      </c>
-      <c r="BI90">
-        <v>1.51</v>
-      </c>
-      <c r="BJ90">
-        <v>2.26</v>
-      </c>
-      <c r="BK90">
-        <v>1.91</v>
-      </c>
-      <c r="BL90">
-        <v>1.76</v>
-      </c>
-      <c r="BM90">
-        <v>2.46</v>
-      </c>
-      <c r="BN90">
-        <v>1.43</v>
-      </c>
-      <c r="BO90">
-        <v>3.42</v>
-      </c>
-      <c r="BP90">
-        <v>1.23</v>
+      <c r="BC94">
+        <v>9</v>
+      </c>
+      <c r="BD94">
+        <v>1.41</v>
+      </c>
+      <c r="BE94">
+        <v>8.9</v>
+      </c>
+      <c r="BF94">
+        <v>3.38</v>
+      </c>
+      <c r="BG94">
+        <v>1.18</v>
+      </c>
+      <c r="BH94">
+        <v>3.85</v>
+      </c>
+      <c r="BI94">
+        <v>1.37</v>
+      </c>
+      <c r="BJ94">
+        <v>2.66</v>
+      </c>
+      <c r="BK94">
+        <v>2.2</v>
+      </c>
+      <c r="BL94">
+        <v>2.06</v>
+      </c>
+      <c r="BM94">
+        <v>2.14</v>
+      </c>
+      <c r="BN94">
+        <v>1.67</v>
+      </c>
+      <c r="BO94">
+        <v>2.74</v>
+      </c>
+      <c r="BP94">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
